--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2137</v>
+        <v>2082</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
         <v>148751600</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>69608</v>
+        <v>71446</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>11 | 2193呎 (4+房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -5593,12 +5593,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>11 | 2193呎 (4+房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -5988,20 +5988,20 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>8 | 1875呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -6011,12 +6011,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>8 | 1875呎 (3房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -6034,12 +6034,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>8 | 1875呎 (3房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -6067,10 +6067,10 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>9 | 2137呎 (4+房)
+          <t>9 | 2082呎 (4+房)
 $14875万
-$69,608/呎
-(26年-08月-04日)</t>
+$71,446/呎
+(26年-09月-09日)</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6134,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,12 +125,6 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -208,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -274,9 +268,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4220,23 +4211,19 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>139332400</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>65200</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4245,12 +4232,12 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4260,7 +4247,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4360,23 +4347,19 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>137195400</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>64200</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4385,12 +4368,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4400,7 +4383,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5862,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5889,7 +5872,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6134,12 +6117,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
-招标单位
--
-(在售)</t>
+$13933万
+$65,200/呎
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -6157,12 +6140,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
-招标单位
--
-(在售)</t>
+$13720万
+$64,200/呎
+(26年-09月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -202,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -268,6 +274,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1175,7 +1184,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1185,12 +1194,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1200,12 +1209,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1215,7 +1224,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1522,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1523,12 +1532,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1538,12 +1547,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1553,7 +1562,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1592,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1593,12 +1602,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1608,12 +1617,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1623,7 +1632,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1938,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1939,12 +1948,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1954,12 +1963,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1969,7 +1978,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1999,7 +2008,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -2009,12 +2018,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2024,12 +2033,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2039,7 +2048,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2358,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2359,12 +2368,12 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2374,12 +2383,12 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2389,7 +2398,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2428,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2429,12 +2438,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2444,12 +2453,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2459,7 +2468,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3882,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3883,12 +3892,12 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3898,12 +3907,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3913,7 +3922,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4632,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4633,12 +4642,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -4648,12 +4657,12 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -4663,7 +4672,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4693,7 +4702,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4703,12 +4712,12 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -4718,12 +4727,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4733,7 +4742,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5367,27 +5376,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -5476,12 +5485,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>10 | 2153呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -5545,20 +5554,20 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>10 | 2153呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>11 | 2193呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5614,20 +5623,20 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>10 | 2153呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>11 | 2193呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5683,20 +5692,20 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>10 | 2153呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>11 | 2193呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5862,27 +5871,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -6040,12 +6049,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>8 | 1875呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -6178,20 +6187,20 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>8 | 1875呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -1592,23 +1592,19 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>145542800</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>67600</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1617,12 +1613,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1632,7 +1628,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5372,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5386,7 +5382,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5554,12 +5550,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>10 | 2153呎 (4+房)
-招标单位
--
-(在售)</t>
+$14554万
+$67,600/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -1329,7 +1329,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -5509,7 +5509,7 @@
           <t>10 | 2153呎 (4+房)
 $15932万
 $74,000/呎
-(26年-09月-02日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -6127,7 +6127,7 @@
           <t>9 | 2137呎 (4+房)
 $13933万
 $65,200/呎
-(26年-09月-14日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2137</v>
+        <v>2082</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4357,14 +4357,14 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
         <v>137195400</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>64200</v>
+        <v>65896</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -5372,27 +5372,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -5512,12 +5512,12 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>11 | 2193呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5581,12 +5581,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>11 | 2193呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -5976,20 +5976,20 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>8 | 1875呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>8 | 1875呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -6022,12 +6022,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>8 | 1875呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -6147,10 +6147,10 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>9 | 2137呎 (4+房)
+          <t>9 | 2082呎 (4+房)
 $13720万
-$64,200/呎
-(26年-09月-14日)</t>
+$65,896/呎
+(26年-10月-07日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -1254,23 +1254,19 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>164475000</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>75000</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1279,12 +1275,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1294,7 +1290,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1593,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -5372,7 +5368,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5382,7 +5378,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5512,12 +5508,12 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>11 | 2193呎 (4+房)
-招标单位
--
-(在售)</t>
+$16448万
+$75,000/呎
+(26年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5551,7 @@
           <t>10 | 2153呎 (4+房)
 $14554万
 $67,600/呎
-(26年-09月-28日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">

--- a/files/港岛-半山区西部-应天.xlsx
+++ b/files/港岛-半山区西部-应天.xlsx
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2955</v>
+        <v>3022</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>380772000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>128857</v>
+        <v>126000</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2133</v>
+        <v>2193</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>155703000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>72997</v>
+        <v>71000</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2097</v>
+        <v>2153</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>165781000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>79056</v>
+        <v>77000</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2849</v>
+        <v>2911</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>362000000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>127062</v>
+        <v>124356</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2082</v>
+        <v>2137</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>157069500</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>75442</v>
+        <v>73500</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2082</v>
+        <v>2137</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>148751600</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>71446</v>
+        <v>69608</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2082</v>
+        <v>2137</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>137195400</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>65896</v>
+        <v>64200</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -5417,9 +5417,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>10 | 2955呎 (4+房)
+          <t>10 | 3022呎 (4+房)
 $38077万
-$128,857/呎
+$126,000/呎
 (26年-07月-13日)</t>
         </is>
       </c>
@@ -5513,7 +5513,7 @@
           <t>11 | 2193呎 (4+房)
 $16448万
 $75,000/呎
-(26年-10月-16日)</t>
+(26年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>10 | 2097呎 (3房)
+          <t>10 | 2153呎 (3房)
 $16578万
-$79,056/呎
+$77,000/呎
 (26年-07月-07日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>11 | 2133呎 (4+房)
+          <t>11 | 2193呎 (4+房)
 $15570万
-$72,997/呎
+$71,000/呎
 (26年-07月-14日)</t>
         </is>
       </c>
@@ -5912,9 +5912,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>8 | 2849呎 (4+房)
+          <t>8 | 2911呎 (4+房)
 $36200万
-$127,062/呎
+$124,356/呎
 (26年-07月-06日)</t>
         </is>
       </c>
@@ -6005,9 +6005,9 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>9 | 2082呎 (4+房)
+          <t>9 | 2137呎 (4+房)
 $15707万
-$75,442/呎
+$73,500/呎
 (26年-08月-06日)</t>
         </is>
       </c>
@@ -6051,9 +6051,9 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>9 | 2082呎 (4+房)
+          <t>9 | 2137呎 (4+房)
 $14875万
-$71,446/呎
+$69,608/呎
 (26年-09月-09日)</t>
         </is>
       </c>
@@ -6143,9 +6143,9 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>9 | 2082呎 (4+房)
+          <t>9 | 2137呎 (4+房)
 $13720万
-$65,896/呎
+$64,200/呎
 (26年-10月-07日)</t>
         </is>
       </c>
